--- a/Entregables/Matriz-Comunicaciones-07-07.xlsx
+++ b/Entregables/Matriz-Comunicaciones-07-07.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://frbautneduar-my.sharepoint.com/personal/jomansilla_frba_utn_edu_ar/Documents/04-Cuarto-Año-2026/Administracion-De-Sistemas-De-Información/TPA/Entregables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="44" documentId="11_F25DC773A252ABDACC1048BDA95E51B25BDE58E7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{187AE363-9819-416F-8F34-FFB891CAFF70}"/>
+  <xr:revisionPtr revIDLastSave="46" documentId="11_F25DC773A252ABDACC1048BDA95E51B25BDE58E7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7D43807-C343-4925-8C2F-FCBF70B0D509}"/>
   <bookViews>
     <workbookView xWindow="6645" yWindow="4185" windowWidth="28800" windowHeight="17235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -373,7 +373,6 @@
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -383,40 +382,41 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -711,340 +711,335 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="B3" s="12"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
     </row>
     <row r="4" spans="1:6" ht="24" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="4" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="5" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="F6" s="10" t="s">
+      <c r="F6" s="6" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E7" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="F7" s="5" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="D8" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="F8" s="6" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="E9" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="F9" s="5" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="D10" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="E10" s="10" t="s">
+      <c r="E10" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F10" s="10" t="s">
+      <c r="F10" s="6" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="9" t="s">
+      <c r="A11" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="D11" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="E11" s="9" t="s">
+      <c r="E11" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="F11" s="9" t="s">
+      <c r="F11" s="5" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="16" t="s">
+      <c r="A13" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="B13" s="12"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-    </row>
-    <row r="14" spans="1:6" ht="36" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+    </row>
+    <row r="14" spans="1:6" ht="24" x14ac:dyDescent="0.25">
+      <c r="A14" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
     </row>
     <row r="15" spans="1:6" ht="24" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="D15" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
     </row>
     <row r="16" spans="1:6" ht="24" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="13" t="s">
+      <c r="B16" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="C16" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D16" s="14" t="s">
+      <c r="D16" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="E16" s="12"/>
-      <c r="F16" s="12"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
     </row>
     <row r="17" spans="1:6" ht="24" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C17" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D17" s="11" t="s">
+      <c r="D17" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
     </row>
     <row r="18" spans="1:6" ht="24" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B18" s="13" t="s">
+      <c r="B18" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C18" s="13" t="s">
+      <c r="C18" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D18" s="14" t="s">
+      <c r="D18" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="B19" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="C19" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D19" s="11" t="s">
+      <c r="D19" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
     </row>
     <row r="20" spans="1:6" ht="24" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B20" s="13" t="s">
+      <c r="B20" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="13" t="s">
+      <c r="C20" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="D20" s="14" t="s">
+      <c r="D20" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
     </row>
     <row r="21" spans="1:6" ht="24" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B21" s="9" t="s">
+      <c r="B21" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="C21" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D21" s="11" t="s">
+      <c r="D21" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="A13:F13"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="D20:F20"/>
     <mergeCell ref="D18:F18"/>
@@ -1053,6 +1048,11 @@
     <mergeCell ref="A14"/>
     <mergeCell ref="D15:F15"/>
     <mergeCell ref="D16:F16"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="A13:F13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
